--- a/data/nzd0472/nzd0472.xlsx
+++ b/data/nzd0472/nzd0472.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G438"/>
+  <dimension ref="A1:G440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12258,6 +12258,60 @@
         <v>337.15</v>
       </c>
       <c r="G438" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>347.21</v>
+      </c>
+      <c r="C439" t="n">
+        <v>342.85</v>
+      </c>
+      <c r="D439" t="n">
+        <v>336.28</v>
+      </c>
+      <c r="E439" t="n">
+        <v>331.9</v>
+      </c>
+      <c r="F439" t="n">
+        <v>337.79</v>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>346.73</v>
+      </c>
+      <c r="C440" t="n">
+        <v>342.14</v>
+      </c>
+      <c r="D440" t="n">
+        <v>336.31</v>
+      </c>
+      <c r="E440" t="n">
+        <v>332.1</v>
+      </c>
+      <c r="F440" t="n">
+        <v>337.91</v>
+      </c>
+      <c r="G440" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12274,7 +12328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B503"/>
+  <dimension ref="A1:B505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17307,6 +17361,26 @@
       </c>
       <c r="B503" t="n">
         <v>-0.7</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>0.29</v>
       </c>
     </row>
   </sheetData>
@@ -17475,28 +17549,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2845023561937978</v>
+        <v>0.2880796966075167</v>
       </c>
       <c r="J2" t="n">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="K2" t="n">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1506724914296282</v>
+        <v>0.1547241231896818</v>
       </c>
       <c r="M2" t="n">
-        <v>3.766865977991939</v>
+        <v>3.769146987506548</v>
       </c>
       <c r="N2" t="n">
-        <v>22.78385054840141</v>
+        <v>22.74869349196965</v>
       </c>
       <c r="O2" t="n">
-        <v>4.773243189740223</v>
+        <v>4.769559045862589</v>
       </c>
       <c r="P2" t="n">
-        <v>335.4190744585681</v>
+        <v>335.3767986440615</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17553,28 +17627,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2415539802631644</v>
+        <v>0.2476798828357209</v>
       </c>
       <c r="J3" t="n">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="K3" t="n">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1195963840139402</v>
+        <v>0.1249686681841014</v>
       </c>
       <c r="M3" t="n">
-        <v>3.852510487448186</v>
+        <v>3.870709406331986</v>
       </c>
       <c r="N3" t="n">
-        <v>21.44896457870781</v>
+        <v>21.55235054288715</v>
       </c>
       <c r="O3" t="n">
-        <v>4.631302687010191</v>
+        <v>4.64245091981457</v>
       </c>
       <c r="P3" t="n">
-        <v>329.3223273456615</v>
+        <v>329.2499332249632</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17631,28 +17705,28 @@
         <v>0.1838</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1773964715145607</v>
+        <v>0.180544721584399</v>
       </c>
       <c r="J4" t="n">
+        <v>439</v>
+      </c>
+      <c r="K4" t="n">
         <v>437</v>
       </c>
-      <c r="K4" t="n">
-        <v>435</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.08031767468945428</v>
+        <v>0.08344096274349588</v>
       </c>
       <c r="M4" t="n">
-        <v>3.512593334356477</v>
+        <v>3.510251602929308</v>
       </c>
       <c r="N4" t="n">
-        <v>18.04794020647729</v>
+        <v>18.01856792476602</v>
       </c>
       <c r="O4" t="n">
-        <v>4.248286737789398</v>
+        <v>4.244828374005952</v>
       </c>
       <c r="P4" t="n">
-        <v>328.0903969717642</v>
+        <v>328.0532063321772</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17709,28 +17783,28 @@
         <v>0.1557</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1813531390711588</v>
+        <v>0.1819117140496209</v>
       </c>
       <c r="J5" t="n">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="K5" t="n">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05800615443174029</v>
+        <v>0.05885525138144121</v>
       </c>
       <c r="M5" t="n">
-        <v>4.291968600120922</v>
+        <v>4.274952917590443</v>
       </c>
       <c r="N5" t="n">
-        <v>26.67093940200243</v>
+        <v>26.55114465915094</v>
       </c>
       <c r="O5" t="n">
-        <v>5.164391484192734</v>
+        <v>5.152780284385405</v>
       </c>
       <c r="P5" t="n">
-        <v>326.5166643068443</v>
+        <v>326.5100625700679</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17787,28 +17861,28 @@
         <v>0.1684</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.05666144423988406</v>
+        <v>-0.05842961018408506</v>
       </c>
       <c r="J6" t="n">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="K6" t="n">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007227927149336177</v>
+        <v>0.007748278629555627</v>
       </c>
       <c r="M6" t="n">
-        <v>3.751466778241908</v>
+        <v>3.74295519779074</v>
       </c>
       <c r="N6" t="n">
-        <v>22.02040145902255</v>
+        <v>21.93680232428951</v>
       </c>
       <c r="O6" t="n">
-        <v>4.69259005870133</v>
+        <v>4.683674019857649</v>
       </c>
       <c r="P6" t="n">
-        <v>341.2976581271897</v>
+        <v>341.3185540034477</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17846,7 +17920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G438"/>
+  <dimension ref="A1:G440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34047,6 +34121,80 @@
         </is>
       </c>
     </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>-45.101906496415616,170.97270528304438</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>-45.102539625517515,170.97264396946753</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>-45.103172277108015,170.97255458061272</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>-45.10380538774937,170.9724930102145</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>-45.10444067748931,170.97256190325524</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>-45.10190639425209,170.97269918564626</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>-45.102539474394256,170.97263495030018</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>-45.103172283493834,170.97255496170848</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>-45.103805430323334,170.97249555088098</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>-45.10444070303301,170.97256342767207</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0472/nzd0472.xlsx
+++ b/data/nzd0472/nzd0472.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G440"/>
+  <dimension ref="A1:G443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12312,6 +12312,87 @@
         <v>337.91</v>
       </c>
       <c r="G440" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:13:47+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>345.74</v>
+      </c>
+      <c r="C441" t="n">
+        <v>341.28</v>
+      </c>
+      <c r="D441" t="n">
+        <v>335.82</v>
+      </c>
+      <c r="E441" t="n">
+        <v>331.94</v>
+      </c>
+      <c r="F441" t="n">
+        <v>337.41</v>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:00+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>345.59</v>
+      </c>
+      <c r="C442" t="n">
+        <v>341.1</v>
+      </c>
+      <c r="D442" t="n">
+        <v>335.81</v>
+      </c>
+      <c r="E442" t="n">
+        <v>331.9</v>
+      </c>
+      <c r="F442" t="n">
+        <v>337.47</v>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:00+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>345.16</v>
+      </c>
+      <c r="C443" t="n">
+        <v>340.83</v>
+      </c>
+      <c r="D443" t="n">
+        <v>335.71</v>
+      </c>
+      <c r="E443" t="n">
+        <v>331.76</v>
+      </c>
+      <c r="F443" t="n">
+        <v>337.62</v>
+      </c>
+      <c r="G443" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12328,7 +12409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B505"/>
+  <dimension ref="A1:B508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17381,6 +17462,36 @@
       </c>
       <c r="B505" t="n">
         <v>0.29</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>
@@ -17549,28 +17660,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2880796966075167</v>
+        <v>0.29126922167943</v>
       </c>
       <c r="J2" t="n">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="K2" t="n">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1547241231896818</v>
+        <v>0.1592560849118587</v>
       </c>
       <c r="M2" t="n">
-        <v>3.769146987506548</v>
+        <v>3.761194954123621</v>
       </c>
       <c r="N2" t="n">
-        <v>22.74869349196965</v>
+        <v>22.63154927724786</v>
       </c>
       <c r="O2" t="n">
-        <v>4.769559045862589</v>
+        <v>4.757262792536046</v>
       </c>
       <c r="P2" t="n">
-        <v>335.3767986440615</v>
+        <v>335.3390127203741</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17627,28 +17738,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2476798828357209</v>
+        <v>0.2546547499922641</v>
       </c>
       <c r="J3" t="n">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="K3" t="n">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1249686681841014</v>
+        <v>0.1318175749940625</v>
       </c>
       <c r="M3" t="n">
-        <v>3.870709406331986</v>
+        <v>3.885005225073107</v>
       </c>
       <c r="N3" t="n">
-        <v>21.55235054288715</v>
+        <v>21.58234505799138</v>
       </c>
       <c r="O3" t="n">
-        <v>4.64245091981457</v>
+        <v>4.645680257829996</v>
       </c>
       <c r="P3" t="n">
-        <v>329.2499332249632</v>
+        <v>329.1672961880438</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17705,28 +17816,28 @@
         <v>0.1838</v>
       </c>
       <c r="I4" t="n">
-        <v>0.180544721584399</v>
+        <v>0.1844260535305983</v>
       </c>
       <c r="J4" t="n">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="K4" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08344096274349588</v>
+        <v>0.08761073774567751</v>
       </c>
       <c r="M4" t="n">
-        <v>3.510251602929308</v>
+        <v>3.503268982067687</v>
       </c>
       <c r="N4" t="n">
-        <v>18.01856792476602</v>
+        <v>17.95051488400345</v>
       </c>
       <c r="O4" t="n">
-        <v>4.244828374005952</v>
+        <v>4.236804796542254</v>
       </c>
       <c r="P4" t="n">
-        <v>328.0532063321772</v>
+        <v>328.0072382009128</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17783,28 +17894,28 @@
         <v>0.1557</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1819117140496209</v>
+        <v>0.1825230567274102</v>
       </c>
       <c r="J5" t="n">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="K5" t="n">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05885525138144121</v>
+        <v>0.06000271617948327</v>
       </c>
       <c r="M5" t="n">
-        <v>4.274952917590443</v>
+        <v>4.248679419361943</v>
       </c>
       <c r="N5" t="n">
-        <v>26.55114465915094</v>
+        <v>26.3723330623269</v>
       </c>
       <c r="O5" t="n">
-        <v>5.152780284385405</v>
+        <v>5.135399990490215</v>
       </c>
       <c r="P5" t="n">
-        <v>326.5100625700679</v>
+        <v>326.5028206847522</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17861,28 +17972,28 @@
         <v>0.1684</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.05842961018408506</v>
+        <v>-0.06147266962049464</v>
       </c>
       <c r="J6" t="n">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="K6" t="n">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007748278629555627</v>
+        <v>0.008674684974035007</v>
       </c>
       <c r="M6" t="n">
-        <v>3.74295519779074</v>
+        <v>3.732267272173231</v>
       </c>
       <c r="N6" t="n">
-        <v>21.93680232428951</v>
+        <v>21.82147130623534</v>
       </c>
       <c r="O6" t="n">
-        <v>4.683674019857649</v>
+        <v>4.671345770357332</v>
       </c>
       <c r="P6" t="n">
-        <v>341.3185540034477</v>
+        <v>341.3546075454259</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17920,7 +18031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G440"/>
+  <dimension ref="A1:G443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34195,6 +34306,117 @@
         </is>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:13:47+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>-45.10190618353879,170.97268660976283</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>-45.102539291342595,170.97262402567503</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>-45.103172179191745,170.97254873714428</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>-45.10380539626416,170.97249351834782</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>-45.10444059660077,170.97255707593524</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:00+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>-45.10190615161242,170.97268470432596</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>-45.10253925302931,170.9726217391256</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>-45.10317217706312,170.97254861011237</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>-45.10380538774937,170.9724930102145</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>-45.10444060937266,170.97255783814364</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:00+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>-45.101906060089945,170.9726792420736</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>-45.10253919555932,170.97261830930145</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>-45.103172155776946,170.97254733979312</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>-45.10380535794756,170.972491231748</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>-45.10444064130235,170.97255974366473</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0472/nzd0472.xlsx
+++ b/data/nzd0472/nzd0472.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G443"/>
+  <dimension ref="A1:G445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12393,6 +12393,60 @@
         <v>337.62</v>
       </c>
       <c r="G443" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:14:04+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>346.06</v>
+      </c>
+      <c r="C444" t="n">
+        <v>341.83</v>
+      </c>
+      <c r="D444" t="n">
+        <v>336.28</v>
+      </c>
+      <c r="E444" t="n">
+        <v>332.58</v>
+      </c>
+      <c r="F444" t="n">
+        <v>339.35</v>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:13+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>346.44</v>
+      </c>
+      <c r="C445" t="n">
+        <v>341.85</v>
+      </c>
+      <c r="D445" t="n">
+        <v>336.6</v>
+      </c>
+      <c r="E445" t="n">
+        <v>332.62</v>
+      </c>
+      <c r="F445" t="n">
+        <v>339.79</v>
+      </c>
+      <c r="G445" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12409,7 +12463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B508"/>
+  <dimension ref="A1:B510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17492,6 +17546,26 @@
       </c>
       <c r="B508" t="n">
         <v>0.6</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>
@@ -17660,28 +17734,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.29126922167943</v>
+        <v>0.2940007543122404</v>
       </c>
       <c r="J2" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K2" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1592560849118587</v>
+        <v>0.1627812218109688</v>
       </c>
       <c r="M2" t="n">
-        <v>3.761194954123621</v>
+        <v>3.759373195579323</v>
       </c>
       <c r="N2" t="n">
-        <v>22.63154927724786</v>
+        <v>22.57055233157257</v>
       </c>
       <c r="O2" t="n">
-        <v>4.757262792536046</v>
+        <v>4.750847538237</v>
       </c>
       <c r="P2" t="n">
-        <v>335.3390127203741</v>
+        <v>335.3064960642099</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17738,28 +17812,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2546547499922641</v>
+        <v>0.2598682100712513</v>
       </c>
       <c r="J3" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K3" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1318175749940625</v>
+        <v>0.1368028828561946</v>
       </c>
       <c r="M3" t="n">
-        <v>3.885005225073107</v>
+        <v>3.897919016981261</v>
       </c>
       <c r="N3" t="n">
-        <v>21.58234505799138</v>
+        <v>21.63374383270646</v>
       </c>
       <c r="O3" t="n">
-        <v>4.645680257829996</v>
+        <v>4.651208857136654</v>
       </c>
       <c r="P3" t="n">
-        <v>329.1672961880438</v>
+        <v>329.1052359073843</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17816,28 +17890,28 @@
         <v>0.1838</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1844260535305983</v>
+        <v>0.1875264523250753</v>
       </c>
       <c r="J4" t="n">
+        <v>444</v>
+      </c>
+      <c r="K4" t="n">
         <v>442</v>
       </c>
-      <c r="K4" t="n">
-        <v>440</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.08761073774567751</v>
+        <v>0.09082890223729356</v>
       </c>
       <c r="M4" t="n">
-        <v>3.503268982067687</v>
+        <v>3.500961932401395</v>
       </c>
       <c r="N4" t="n">
-        <v>17.95051488400345</v>
+        <v>17.92221943744351</v>
       </c>
       <c r="O4" t="n">
-        <v>4.236804796542254</v>
+        <v>4.233464235994384</v>
       </c>
       <c r="P4" t="n">
-        <v>328.0072382009128</v>
+        <v>327.9703441460007</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17894,28 +17968,28 @@
         <v>0.1557</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1825230567274102</v>
+        <v>0.1835660922463384</v>
       </c>
       <c r="J5" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K5" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06000271617948327</v>
+        <v>0.06116441845366893</v>
       </c>
       <c r="M5" t="n">
-        <v>4.248679419361943</v>
+        <v>4.234137869972945</v>
       </c>
       <c r="N5" t="n">
-        <v>26.3723330623269</v>
+        <v>26.25948813782564</v>
       </c>
       <c r="O5" t="n">
-        <v>5.135399990490215</v>
+        <v>5.124401246762947</v>
       </c>
       <c r="P5" t="n">
-        <v>326.5028206847522</v>
+        <v>326.4904044762364</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17972,28 +18046,28 @@
         <v>0.1684</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.06147266962049464</v>
+        <v>-0.06158039414434069</v>
       </c>
       <c r="J6" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K6" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008674684974035007</v>
+        <v>0.008784852748189187</v>
       </c>
       <c r="M6" t="n">
-        <v>3.732267272173231</v>
+        <v>3.716433931231164</v>
       </c>
       <c r="N6" t="n">
-        <v>21.82147130623534</v>
+        <v>21.72346073253263</v>
       </c>
       <c r="O6" t="n">
-        <v>4.671345770357332</v>
+        <v>4.660843349924199</v>
       </c>
       <c r="P6" t="n">
-        <v>341.3546075454259</v>
+        <v>341.3558888074057</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18031,7 +18105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G443"/>
+  <dimension ref="A1:G445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34417,6 +34491,80 @@
         </is>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:14:04+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>-45.10190625164828,170.97269067469483</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>-45.10253940841064,170.9726310123539</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>-45.103172277108015,170.97255458061272</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>-45.103805532500594,170.9725016484805</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>-45.10444100955588,170.97258172067438</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:13+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>-45.10190633252814,170.9726955018016</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>-45.102539412667646,170.97263126641496</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>-45.103172345223484,170.97255864563428</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>-45.10380554101537,170.97250215661376</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>-45.104441103215066,170.97258731020293</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
